--- a/data_lake/macro/USA/FED Target Rate.xlsx
+++ b/data_lake/macro/USA/FED Target Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/macro/USA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDA18D1-76B1-46F8-B706-DFE5518E8E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E596671-1AD5-E04E-90D8-BE2821FE4E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fed Target Rate" sheetId="1" r:id="rId1"/>
@@ -73,28 +73,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -102,7 +102,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -146,33 +146,33 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="백분율" xfId="1" builtinId="5"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -190,7 +190,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2109,6 +2109,9 @@
                 </c:pt>
                 <c:pt idx="298">
                   <c:v>3.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.04</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3153,19 +3156,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G311"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.8984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -3188,7 +3191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>30221</v>
       </c>
@@ -3221,7 +3224,7 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>30225</v>
       </c>
@@ -3257,7 +3260,7 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>30231</v>
       </c>
@@ -3278,7 +3281,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>30274</v>
       </c>
@@ -3299,7 +3302,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>30299</v>
       </c>
@@ -3320,7 +3323,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>30406</v>
       </c>
@@ -3341,7 +3344,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>30461</v>
       </c>
@@ -3362,7 +3365,7 @@
         <v>8.6199999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>30491</v>
       </c>
@@ -3383,7 +3386,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>30511</v>
       </c>
@@ -3404,7 +3407,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>30517</v>
       </c>
@@ -3425,7 +3428,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>30539</v>
       </c>
@@ -3446,7 +3449,7 @@
         <v>9.4299999999999995E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>30545</v>
       </c>
@@ -3467,7 +3470,7 @@
         <v>9.5600000000000004E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>30574</v>
       </c>
@@ -3488,7 +3491,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>30770</v>
       </c>
@@ -3509,7 +3512,7 @@
         <v>9.3700000000000006E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>30868</v>
       </c>
@@ -3530,7 +3533,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>30882</v>
       </c>
@@ -3551,7 +3554,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>30903</v>
       </c>
@@ -3572,7 +3575,7 @@
         <v>0.1125</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>30945</v>
       </c>
@@ -3593,7 +3596,7 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>30952</v>
       </c>
@@ -3614,7 +3617,7 @@
         <v>0.1125</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>30966</v>
       </c>
@@ -3635,7 +3638,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>30973</v>
       </c>
@@ -3656,7 +3659,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>30994</v>
       </c>
@@ -3677,7 +3680,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>31009</v>
       </c>
@@ -3698,7 +3701,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>31022</v>
       </c>
@@ -3719,7 +3722,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>31035</v>
       </c>
@@ -3740,7 +3743,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>31040</v>
       </c>
@@ -3761,7 +3764,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>31071</v>
       </c>
@@ -3782,7 +3785,7 @@
         <v>8.1199999999999994E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>31092</v>
       </c>
@@ -3803,7 +3806,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>31134</v>
       </c>
@@ -3824,7 +3827,7 @@
         <v>8.3699999999999997E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
         <v>31162</v>
       </c>
@@ -3845,7 +3848,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>31187</v>
       </c>
@@ -3866,7 +3869,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>31239</v>
       </c>
@@ -3887,7 +3890,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>31253</v>
       </c>
@@ -3908,7 +3911,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>31280</v>
       </c>
@@ -3929,7 +3932,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>31296</v>
       </c>
@@ -3950,7 +3953,7 @@
         <v>7.8100000000000003E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <v>31399</v>
       </c>
@@ -3971,7 +3974,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>31478</v>
       </c>
@@ -3992,7 +3995,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>31504</v>
       </c>
@@ -4013,7 +4016,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>31523</v>
       </c>
@@ -4034,7 +4037,7 @@
         <v>7.3099999999999998E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>31554</v>
       </c>
@@ -4055,7 +4058,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>31568</v>
       </c>
@@ -4076,7 +4079,7 @@
         <v>6.8099999999999994E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>31604</v>
       </c>
@@ -4097,7 +4100,7 @@
         <v>6.8699999999999997E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>31645</v>
       </c>
@@ -4118,7 +4121,7 @@
         <v>6.3700000000000007E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
         <v>31782</v>
       </c>
@@ -4139,7 +4142,7 @@
         <v>5.8700000000000002E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>31897</v>
       </c>
@@ -4160,7 +4163,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>31919</v>
       </c>
@@ -4181,7 +4184,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>31960</v>
       </c>
@@ -4202,7 +4205,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
         <v>32016</v>
       </c>
@@ -4223,7 +4226,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>32023</v>
       </c>
@@ -4244,7 +4247,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
         <v>32024</v>
       </c>
@@ -4265,7 +4268,7 @@
         <v>6.8699999999999997E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>32044</v>
       </c>
@@ -4286,7 +4289,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="7">
         <v>32085</v>
       </c>
@@ -4307,7 +4310,7 @@
         <v>7.3099999999999998E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>32170</v>
       </c>
@@ -4328,7 +4331,7 @@
         <v>6.8099999999999994E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="7">
         <v>32184</v>
       </c>
@@ -4349,7 +4352,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>32232</v>
       </c>
@@ -4370,7 +4373,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="7">
         <v>32272</v>
       </c>
@@ -4391,7 +4394,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>32288</v>
       </c>
@@ -4412,7 +4415,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="7">
         <v>32316</v>
       </c>
@@ -4433,7 +4436,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>32325</v>
       </c>
@@ -4454,7 +4457,7 @@
         <v>7.4300000000000005E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="7">
         <v>32343</v>
       </c>
@@ -4475,7 +4478,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>32363</v>
       </c>
@@ -4496,7 +4499,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="7">
         <v>32364</v>
       </c>
@@ -4517,7 +4520,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>32464</v>
       </c>
@@ -4538,7 +4541,7 @@
         <v>8.1199999999999994E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="7">
         <v>32469</v>
       </c>
@@ -4559,7 +4562,7 @@
         <v>8.3099999999999993E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="7">
         <v>32492</v>
       </c>
@@ -4580,7 +4583,7 @@
         <v>8.3699999999999997E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="7">
         <v>32513</v>
       </c>
@@ -4616,7 +4619,7 @@
         <v>8.6800000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="7">
         <v>32548</v>
       </c>
@@ -4637,7 +4640,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="7">
         <v>32553</v>
       </c>
@@ -4658,7 +4661,7 @@
         <v>9.1200000000000003E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="7">
         <v>32563</v>
       </c>
@@ -4679,7 +4682,7 @@
         <v>9.3100000000000002E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="7">
         <v>32645</v>
       </c>
@@ -4700,7 +4703,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="7">
         <v>32665</v>
       </c>
@@ -4721,7 +4724,7 @@
         <v>9.8100000000000007E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="7">
         <v>32696</v>
       </c>
@@ -4742,7 +4745,7 @@
         <v>9.5600000000000004E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="7">
         <v>32716</v>
       </c>
@@ -4763,7 +4766,7 @@
         <v>9.3100000000000002E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="7">
         <v>32800</v>
       </c>
@@ -4784,7 +4787,7 @@
         <v>9.06E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="7">
         <v>32818</v>
       </c>
@@ -4805,7 +4808,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="7">
         <v>32862</v>
       </c>
@@ -4826,7 +4829,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
         <v>33067</v>
       </c>
@@ -4847,7 +4850,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="7">
         <v>33175</v>
       </c>
@@ -4868,7 +4871,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="7">
         <v>33191</v>
       </c>
@@ -4889,7 +4892,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="7">
         <v>33214</v>
       </c>
@@ -4910,7 +4913,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="7">
         <v>33226</v>
       </c>
@@ -4931,7 +4934,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="7">
         <v>33247</v>
       </c>
@@ -4952,7 +4955,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="7">
         <v>33270</v>
       </c>
@@ -4973,7 +4976,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="7">
         <v>33305</v>
       </c>
@@ -4994,7 +4997,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="7">
         <v>33358</v>
       </c>
@@ -5015,7 +5018,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="7">
         <v>33456</v>
       </c>
@@ -5036,7 +5039,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="7">
         <v>33494</v>
       </c>
@@ -5057,7 +5060,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="7">
         <v>33542</v>
       </c>
@@ -5078,7 +5081,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="7">
         <v>33548</v>
       </c>
@@ -5099,7 +5102,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="7">
         <v>33578</v>
       </c>
@@ -5120,7 +5123,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="7">
         <v>33592</v>
       </c>
@@ -5141,7 +5144,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="7">
         <v>33703</v>
       </c>
@@ -5162,7 +5165,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="7">
         <v>33787</v>
       </c>
@@ -5183,7 +5186,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="7">
         <v>33851</v>
       </c>
@@ -5204,7 +5207,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
         <v>34369</v>
       </c>
@@ -5225,7 +5228,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <v>34415</v>
       </c>
@@ -5246,7 +5249,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <v>34442</v>
       </c>
@@ -5267,7 +5270,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <v>34471</v>
       </c>
@@ -5288,7 +5291,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <v>34562</v>
       </c>
@@ -5309,7 +5312,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <v>34653</v>
       </c>
@@ -5330,7 +5333,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <v>34731</v>
       </c>
@@ -5351,7 +5354,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <v>34886</v>
       </c>
@@ -5372,7 +5375,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <v>35052</v>
       </c>
@@ -5393,7 +5396,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <v>35095</v>
       </c>
@@ -5414,7 +5417,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <v>35514</v>
       </c>
@@ -5435,7 +5438,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <v>36067</v>
       </c>
@@ -5456,7 +5459,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <v>36083</v>
       </c>
@@ -5477,7 +5480,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <v>36116</v>
       </c>
@@ -5498,7 +5501,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <v>36341</v>
       </c>
@@ -5519,7 +5522,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <v>36396</v>
       </c>
@@ -5540,7 +5543,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <v>36480</v>
       </c>
@@ -5561,7 +5564,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="7">
         <v>36558</v>
       </c>
@@ -5582,7 +5585,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="7">
         <v>36606</v>
       </c>
@@ -5603,7 +5606,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="7">
         <v>36662</v>
       </c>
@@ -5624,7 +5627,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="7">
         <v>36894</v>
       </c>
@@ -5645,7 +5648,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="7">
         <v>36922</v>
       </c>
@@ -5666,7 +5669,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="7">
         <v>36970</v>
       </c>
@@ -5687,7 +5690,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="7">
         <v>36999</v>
       </c>
@@ -5708,7 +5711,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="7">
         <v>37026</v>
       </c>
@@ -5729,7 +5732,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="7">
         <v>37069</v>
       </c>
@@ -5750,7 +5753,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="7">
         <v>37124</v>
       </c>
@@ -5771,7 +5774,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="7">
         <v>37151</v>
       </c>
@@ -5792,7 +5795,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="7">
         <v>37166</v>
       </c>
@@ -5813,7 +5816,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="7">
         <v>37201</v>
       </c>
@@ -5834,7 +5837,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="7">
         <v>37236</v>
       </c>
@@ -5855,7 +5858,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="7">
         <v>37566</v>
       </c>
@@ -5876,7 +5879,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="7">
         <v>37797</v>
       </c>
@@ -5897,7 +5900,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="7">
         <v>38168</v>
       </c>
@@ -5918,7 +5921,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="7">
         <v>38209</v>
       </c>
@@ -5939,7 +5942,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="7">
         <v>38251</v>
       </c>
@@ -5975,7 +5978,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="7">
         <v>38301</v>
       </c>
@@ -5996,7 +5999,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="7">
         <v>38335</v>
       </c>
@@ -6017,7 +6020,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="7">
         <v>38385</v>
       </c>
@@ -6038,7 +6041,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="7">
         <v>38433</v>
       </c>
@@ -6059,7 +6062,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="7">
         <v>38475</v>
       </c>
@@ -6080,7 +6083,7 @@
         <v>2.75E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="7">
         <v>38533</v>
       </c>
@@ -6101,7 +6104,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="7">
         <v>38573</v>
       </c>
@@ -6122,7 +6125,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="7">
         <v>38615</v>
       </c>
@@ -6143,7 +6146,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="7">
         <v>38657</v>
       </c>
@@ -6164,7 +6167,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="7">
         <v>38699</v>
       </c>
@@ -6185,7 +6188,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="7">
         <v>38748</v>
       </c>
@@ -6206,7 +6209,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="7">
         <v>38804</v>
       </c>
@@ -6227,7 +6230,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="7">
         <v>38847</v>
       </c>
@@ -6248,7 +6251,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="7">
         <v>38897</v>
       </c>
@@ -6269,7 +6272,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="7">
         <v>39343</v>
       </c>
@@ -6290,7 +6293,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="7">
         <v>39386</v>
       </c>
@@ -6311,7 +6314,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="7">
         <v>39427</v>
       </c>
@@ -6332,7 +6335,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="7">
         <v>39469</v>
       </c>
@@ -6353,7 +6356,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="7">
         <v>39477</v>
       </c>
@@ -6374,7 +6377,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <v>39525</v>
       </c>
@@ -6398,7 +6401,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <v>39568</v>
       </c>
@@ -6422,7 +6425,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <v>39624</v>
       </c>
@@ -6446,7 +6449,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <v>39665</v>
       </c>
@@ -6467,7 +6470,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <v>39707</v>
       </c>
@@ -6491,7 +6494,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <v>39729</v>
       </c>
@@ -6512,7 +6515,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <v>39750</v>
       </c>
@@ -6536,7 +6539,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <v>39798</v>
       </c>
@@ -6560,7 +6563,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="7">
         <v>39841</v>
       </c>
@@ -6584,7 +6587,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="7">
         <v>39890</v>
       </c>
@@ -6608,7 +6611,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="7">
         <v>39932</v>
       </c>
@@ -6632,7 +6635,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="7">
         <v>39988</v>
       </c>
@@ -6656,7 +6659,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="7">
         <v>40037</v>
       </c>
@@ -6680,7 +6683,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="7">
         <v>40079</v>
       </c>
@@ -6704,7 +6707,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="7">
         <v>40121</v>
       </c>
@@ -6728,7 +6731,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="7">
         <v>40163</v>
       </c>
@@ -6752,7 +6755,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="7">
         <v>40205</v>
       </c>
@@ -6776,7 +6779,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="7">
         <v>40253</v>
       </c>
@@ -6800,7 +6803,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="7">
         <v>40296</v>
       </c>
@@ -6824,7 +6827,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="7">
         <v>40352</v>
       </c>
@@ -6848,7 +6851,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="7">
         <v>40400</v>
       </c>
@@ -6872,7 +6875,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="7">
         <v>40442</v>
       </c>
@@ -6896,7 +6899,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <v>40485</v>
       </c>
@@ -6920,7 +6923,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <v>40526</v>
       </c>
@@ -6944,7 +6947,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <v>40569</v>
       </c>
@@ -6968,7 +6971,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <v>40617</v>
       </c>
@@ -6992,7 +6995,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <v>40660</v>
       </c>
@@ -7016,7 +7019,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <v>40716</v>
       </c>
@@ -7040,7 +7043,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <v>40764</v>
       </c>
@@ -7064,7 +7067,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <v>40807</v>
       </c>
@@ -7088,7 +7091,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <v>40849</v>
       </c>
@@ -7112,7 +7115,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <v>40890</v>
       </c>
@@ -7136,7 +7139,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <v>40933</v>
       </c>
@@ -7160,7 +7163,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <v>40981</v>
       </c>
@@ -7184,7 +7187,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="7">
         <v>41024</v>
       </c>
@@ -7208,7 +7211,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" s="7">
         <v>41080</v>
       </c>
@@ -7232,7 +7235,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="7">
         <v>41122</v>
       </c>
@@ -7256,7 +7259,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" s="7">
         <v>41165</v>
       </c>
@@ -7280,7 +7283,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="7">
         <v>41206</v>
       </c>
@@ -7304,7 +7307,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" s="7">
         <v>41255</v>
       </c>
@@ -7328,7 +7331,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" s="7">
         <v>41304</v>
       </c>
@@ -7352,7 +7355,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="7">
         <v>41353</v>
       </c>
@@ -7376,7 +7379,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="7">
         <v>41395</v>
       </c>
@@ -7400,7 +7403,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="7">
         <v>41444</v>
       </c>
@@ -7424,7 +7427,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" s="7">
         <v>41486</v>
       </c>
@@ -7463,7 +7466,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" s="7">
         <v>41535</v>
       </c>
@@ -7487,7 +7490,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="7">
         <v>41577</v>
       </c>
@@ -7511,7 +7514,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" s="7">
         <v>41626</v>
       </c>
@@ -7535,7 +7538,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="7">
         <v>41668</v>
       </c>
@@ -7559,7 +7562,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" s="7">
         <v>41717</v>
       </c>
@@ -7583,7 +7586,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="7">
         <v>41759</v>
       </c>
@@ -7607,7 +7610,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="7">
         <v>41808</v>
       </c>
@@ -7631,7 +7634,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="7">
         <v>41850</v>
       </c>
@@ -7655,7 +7658,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="7">
         <v>41899</v>
       </c>
@@ -7679,7 +7682,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" s="7">
         <v>41941</v>
       </c>
@@ -7703,7 +7706,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="7">
         <v>41990</v>
       </c>
@@ -7727,7 +7730,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="7">
         <v>42032</v>
       </c>
@@ -7751,7 +7754,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <v>42081</v>
       </c>
@@ -7775,7 +7778,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="7">
         <v>42123</v>
       </c>
@@ -7799,7 +7802,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="7">
         <v>42172</v>
       </c>
@@ -7823,7 +7826,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="7">
         <v>42214</v>
       </c>
@@ -7847,7 +7850,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="7">
         <v>42264</v>
       </c>
@@ -7871,7 +7874,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" s="7">
         <v>42305</v>
       </c>
@@ -7895,7 +7898,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="7">
         <v>42354</v>
       </c>
@@ -7919,7 +7922,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" s="7">
         <v>42396</v>
       </c>
@@ -7943,7 +7946,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="7">
         <v>42445</v>
       </c>
@@ -7967,7 +7970,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="7">
         <v>42487</v>
       </c>
@@ -7991,7 +7994,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="7">
         <v>42536</v>
       </c>
@@ -8015,7 +8018,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="7">
         <v>42578</v>
       </c>
@@ -8039,7 +8042,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="7">
         <v>42634</v>
       </c>
@@ -8063,7 +8066,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="7">
         <v>42676</v>
       </c>
@@ -8087,7 +8090,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="7">
         <v>42718</v>
       </c>
@@ -8111,7 +8114,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="7">
         <v>42767</v>
       </c>
@@ -8135,7 +8138,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="7">
         <v>42809</v>
       </c>
@@ -8159,7 +8162,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="7">
         <v>42858</v>
       </c>
@@ -8183,7 +8186,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="7">
         <v>42900</v>
       </c>
@@ -8207,7 +8210,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="7">
         <v>42942</v>
       </c>
@@ -8231,7 +8234,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="7">
         <v>42998</v>
       </c>
@@ -8255,7 +8258,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="7">
         <v>43040</v>
       </c>
@@ -8279,7 +8282,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="7">
         <v>43082</v>
       </c>
@@ -8303,7 +8306,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="7">
         <v>43131</v>
       </c>
@@ -8327,7 +8330,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="7">
         <v>43180</v>
       </c>
@@ -8351,7 +8354,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="7">
         <v>43222</v>
       </c>
@@ -8375,7 +8378,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="7">
         <v>43264</v>
       </c>
@@ -8399,7 +8402,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="7">
         <v>43313</v>
       </c>
@@ -8423,7 +8426,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="7">
         <v>43369</v>
       </c>
@@ -8447,7 +8450,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="7">
         <v>43412</v>
       </c>
@@ -8471,7 +8474,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="7">
         <v>43453</v>
       </c>
@@ -8495,7 +8498,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="7">
         <v>43495</v>
       </c>
@@ -8519,7 +8522,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="7">
         <v>43544</v>
       </c>
@@ -8543,7 +8546,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="7">
         <v>43586</v>
       </c>
@@ -8567,7 +8570,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" s="7">
         <v>43635</v>
       </c>
@@ -8591,7 +8594,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" s="7">
         <v>43677</v>
       </c>
@@ -8615,7 +8618,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" s="7">
         <v>43726</v>
       </c>
@@ -8639,7 +8642,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" s="7">
         <v>43768</v>
       </c>
@@ -8663,7 +8666,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" s="7">
         <v>43810</v>
       </c>
@@ -8687,7 +8690,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="7">
         <v>43859</v>
       </c>
@@ -8711,7 +8714,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="7">
         <v>43893</v>
       </c>
@@ -8732,7 +8735,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" s="7">
         <v>43905</v>
       </c>
@@ -8753,7 +8756,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" s="7">
         <v>43950</v>
       </c>
@@ -8777,7 +8780,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" s="7">
         <v>43992</v>
       </c>
@@ -8801,7 +8804,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" s="7">
         <v>44041</v>
       </c>
@@ -8825,7 +8828,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" s="7">
         <v>44090</v>
       </c>
@@ -8849,7 +8852,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="7">
         <v>44140</v>
       </c>
@@ -8873,7 +8876,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="7">
         <v>44181</v>
       </c>
@@ -8897,7 +8900,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" s="7">
         <v>44223</v>
       </c>
@@ -8921,7 +8924,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="7">
         <v>44272</v>
       </c>
@@ -8945,7 +8948,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="7">
         <v>44314</v>
       </c>
@@ -8969,7 +8972,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="7">
         <v>44363</v>
       </c>
@@ -9008,7 +9011,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="7">
         <v>44405</v>
       </c>
@@ -9032,7 +9035,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="7">
         <v>44461</v>
       </c>
@@ -9056,7 +9059,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="7">
         <v>44503</v>
       </c>
@@ -9080,7 +9083,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="7">
         <v>44545</v>
       </c>
@@ -9104,7 +9107,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="7">
         <v>44587</v>
       </c>
@@ -9128,7 +9131,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="7">
         <v>44636</v>
       </c>
@@ -9152,7 +9155,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="7">
         <v>44685</v>
       </c>
@@ -9176,7 +9179,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="7">
         <v>44727</v>
       </c>
@@ -9200,7 +9203,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="7">
         <v>44769</v>
       </c>
@@ -9224,7 +9227,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="7">
         <v>44825</v>
       </c>
@@ -9248,7 +9251,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="7">
         <v>44867</v>
       </c>
@@ -9272,7 +9275,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="7">
         <v>44909</v>
       </c>
@@ -9296,7 +9299,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="7">
         <v>44958</v>
       </c>
@@ -9320,7 +9323,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" s="7">
         <v>45007</v>
       </c>
@@ -9344,7 +9347,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" s="7">
         <v>45049</v>
       </c>
@@ -9368,7 +9371,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" s="7">
         <v>45091</v>
       </c>
@@ -9392,7 +9395,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="7">
         <v>45133</v>
       </c>
@@ -9416,7 +9419,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="7">
         <v>45189</v>
       </c>
@@ -9440,7 +9443,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="7">
         <v>45231</v>
       </c>
@@ -9464,7 +9467,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" s="7">
         <v>45273</v>
       </c>
@@ -9488,7 +9491,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" s="7">
         <v>45322</v>
       </c>
@@ -9512,7 +9515,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="7">
         <v>45371</v>
       </c>
@@ -9536,7 +9539,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="7">
         <v>45413</v>
       </c>
@@ -9560,7 +9563,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" s="7">
         <v>45455</v>
       </c>
@@ -9584,7 +9587,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" s="7">
         <v>45504</v>
       </c>
@@ -9608,7 +9611,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="7">
         <v>45553</v>
       </c>
@@ -9632,7 +9635,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="7">
         <v>45603</v>
       </c>
@@ -9656,7 +9659,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="7">
         <v>45644</v>
       </c>
@@ -9680,7 +9683,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" s="7">
         <v>45686</v>
       </c>
@@ -9704,7 +9707,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289" s="7">
         <v>45735</v>
       </c>
@@ -9728,7 +9731,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290" s="7">
         <v>45784</v>
       </c>
@@ -9752,7 +9755,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291" s="7">
         <v>45826</v>
       </c>
@@ -9776,7 +9779,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292" s="7">
         <v>45868</v>
       </c>
@@ -9800,7 +9803,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293" s="7">
         <v>45917</v>
       </c>
@@ -9824,7 +9827,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="7">
         <v>45959</v>
       </c>
@@ -9848,7 +9851,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="7">
         <v>46001</v>
       </c>
@@ -9872,7 +9875,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" s="7">
         <v>46050</v>
       </c>
@@ -9911,7 +9914,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" s="7">
         <v>46099</v>
       </c>
@@ -9935,7 +9938,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="7">
         <v>46141</v>
       </c>
@@ -9959,7 +9962,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="7">
         <v>46190</v>
       </c>
@@ -9998,7 +10001,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" s="7">
         <v>46232</v>
       </c>
@@ -10022,7 +10025,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301" s="7">
         <v>46281</v>
       </c>
@@ -10036,8 +10039,17 @@
         <f t="shared" si="6"/>
         <v>UTC-4</v>
       </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E301" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="F301" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="G301" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="7">
         <v>46323</v>
       </c>
@@ -10052,7 +10064,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303" s="7">
         <v>46365</v>
       </c>
@@ -10067,7 +10079,7 @@
         <v>UTC-5</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304" s="7">
         <v>46414</v>
       </c>
@@ -10082,7 +10094,7 @@
         <v>UTC-5</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A305" s="7">
         <v>46463</v>
       </c>
@@ -10112,7 +10124,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A306" s="7">
         <v>46140</v>
       </c>
@@ -10127,7 +10139,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A307" s="7">
         <v>46547</v>
       </c>
@@ -10142,7 +10154,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A308" s="7">
         <v>46596</v>
       </c>
@@ -10157,7 +10169,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A309" s="7">
         <v>46645</v>
       </c>
@@ -10172,7 +10184,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A310" s="7">
         <v>46687</v>
       </c>
@@ -10187,7 +10199,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A311" s="7">
         <v>46729</v>
       </c>
@@ -10212,7 +10224,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9EAB5-0149-4548-96A8-B9F3C1083AD8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10223,12 +10235,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E03F4A-9B60-4F24-A253-F9B33163B43A}">
   <dimension ref="B2:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
